--- a/data/trans_orig/P36B06-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B06-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de fruta fresca en 2007</t>
+          <t>Población según la frecuencia de consumo de fruta fresca (excluyendo zumos) en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18302</t>
+          <t>17670</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4809</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20166</t>
+          <t>20234</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13958</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33147</t>
+          <t>30569</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17258</t>
+          <t>17992</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20424</t>
+          <t>19778</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44222</t>
+          <t>41942</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51204</t>
+          <t>49546</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>81521</t>
+          <t>80250</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25188</t>
+          <t>25409</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48303</t>
+          <t>47541</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83556</t>
+          <t>82581</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>121036</t>
+          <t>120798</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>114837</t>
+          <t>114864</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>153401</t>
+          <t>154785</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72299</t>
+          <t>72056</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102948</t>
+          <t>104873</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>196908</t>
+          <t>196952</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>246852</t>
+          <t>247162</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,67%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>224706</t>
+          <t>225159</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>268313</t>
+          <t>269283</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>153470</t>
+          <t>150041</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>189558</t>
+          <t>187108</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>389851</t>
+          <t>389409</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>447916</t>
+          <t>444366</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>56,94%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>13838</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7429</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21975</t>
+          <t>20923</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12258</t>
+          <t>12182</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29502</t>
+          <t>30587</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12553</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30425</t>
+          <t>30198</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7832</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22994</t>
+          <t>22407</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23011</t>
+          <t>21993</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45076</t>
+          <t>44299</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39841</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64956</t>
+          <t>65953</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42325</t>
+          <t>42531</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69547</t>
+          <t>70254</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>88927</t>
+          <t>87799</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>126341</t>
+          <t>124915</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89093</t>
+          <t>87263</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125132</t>
+          <t>122776</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84534</t>
+          <t>83945</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>119328</t>
+          <t>117408</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>183115</t>
+          <t>180160</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>232656</t>
+          <t>231240</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>161701</t>
+          <t>163195</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>201088</t>
+          <t>202140</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>169762</t>
+          <t>169376</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>207525</t>
+          <t>209306</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>344441</t>
+          <t>346308</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>399418</t>
+          <t>401796</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,45%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7297</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21944</t>
+          <t>22506</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>2311</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14523</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11871</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29413</t>
+          <t>28893</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22077</t>
+          <t>22348</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45239</t>
+          <t>44845</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>959</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12446</t>
+          <t>11552</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24687</t>
+          <t>24446</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48894</t>
+          <t>51443</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>65311</t>
+          <t>67451</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>99897</t>
+          <t>100888</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13793</t>
+          <t>13563</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30660</t>
+          <t>31764</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>85558</t>
+          <t>86706</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>121473</t>
+          <t>124554</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,54%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>139370</t>
+          <t>141446</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>184858</t>
+          <t>185495</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34603</t>
+          <t>34350</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57096</t>
+          <t>57720</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>181774</t>
+          <t>183761</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>232472</t>
+          <t>234401</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231710</t>
+          <t>229028</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>278903</t>
+          <t>276275</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78529</t>
+          <t>77849</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>104790</t>
+          <t>102598</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>317841</t>
+          <t>315656</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>372290</t>
+          <t>368867</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>51,94%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12992</t>
+          <t>12844</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31954</t>
+          <t>32201</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20893</t>
+          <t>20505</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22386</t>
+          <t>22400</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46746</t>
+          <t>46669</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>51901</t>
+          <t>52271</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>83528</t>
+          <t>85739</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24028</t>
+          <t>24599</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>46736</t>
+          <t>47849</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>82934</t>
+          <t>82373</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>122891</t>
+          <t>121958</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>166175</t>
+          <t>168502</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>220685</t>
+          <t>219138</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>71483</t>
+          <t>70733</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>105171</t>
+          <t>105075</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>249497</t>
+          <t>249648</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>312296</t>
+          <t>314724</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>312330</t>
+          <t>308352</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>379519</t>
+          <t>374487</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>160708</t>
+          <t>160239</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>206186</t>
+          <t>205984</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>487972</t>
+          <t>483245</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>561638</t>
+          <t>563782</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>581515</t>
+          <t>579398</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>654819</t>
+          <t>650267</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>371098</t>
+          <t>368984</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>424231</t>
+          <t>422794</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>972492</t>
+          <t>966090</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1057318</t>
+          <t>1052651</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>53,94%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>22078</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>19530</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15359</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>35028</t>
+          <t>35672</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14173</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>32802</t>
+          <t>34372</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11530</t>
+          <t>11006</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29737</t>
+          <t>28608</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>29795</t>
+          <t>29735</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>55314</t>
+          <t>55519</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>54887</t>
+          <t>55664</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>85184</t>
+          <t>85521</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>67501</t>
+          <t>68163</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>99745</t>
+          <t>101096</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>130122</t>
+          <t>131706</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>175306</t>
+          <t>176595</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>87218</t>
+          <t>86364</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>122323</t>
+          <t>120108</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>130124</t>
+          <t>131112</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>175322</t>
+          <t>174112</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>225950</t>
+          <t>230638</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>284658</t>
+          <t>283900</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,92%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>125265</t>
+          <t>124695</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>161473</t>
+          <t>159498</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>278102</t>
+          <t>275640</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>327169</t>
+          <t>323670</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>413575</t>
+          <t>414212</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>475396</t>
+          <t>473013</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,51%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>7030</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>20112</t>
+          <t>21041</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>11879</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>29088</t>
+          <t>28214</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>21376</t>
+          <t>21372</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>43279</t>
+          <t>43781</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>17722</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>36173</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>21706</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>43980</t>
+          <t>43120</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>43344</t>
+          <t>45218</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>73302</t>
+          <t>73583</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>44412</t>
+          <t>44546</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>71215</t>
+          <t>71619</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>139167</t>
+          <t>138524</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>184881</t>
+          <t>185212</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>193701</t>
+          <t>191476</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>247799</t>
+          <t>245857</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>80017</t>
+          <t>78933</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>110972</t>
+          <t>110713</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>269309</t>
+          <t>271380</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>332126</t>
+          <t>329869</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>363904</t>
+          <t>358610</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>425369</t>
+          <t>427206</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>91472</t>
+          <t>90966</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>123611</t>
+          <t>123255</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>703466</t>
+          <t>698831</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>767973</t>
+          <t>765462</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>806072</t>
+          <t>807866</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>883688</t>
+          <t>884255</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,24%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>57325</t>
+          <t>58535</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>93482</t>
+          <t>92980</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>49464</t>
+          <t>48462</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>81143</t>
+          <t>80301</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>115245</t>
+          <t>115073</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>158452</t>
+          <t>161661</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>162660</t>
+          <t>162186</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>213873</t>
+          <t>215276</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>92047</t>
+          <t>92887</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>135440</t>
+          <t>134057</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>266189</t>
+          <t>268129</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>335707</t>
+          <t>335140</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>473226</t>
+          <t>477838</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>556726</t>
+          <t>564063</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>406337</t>
+          <t>407156</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>484705</t>
+          <t>483235</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>911035</t>
+          <t>906167</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1023351</t>
+          <t>1022088</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>888539</t>
+          <t>888126</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>996202</t>
+          <t>992544</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>817719</t>
+          <t>827480</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>922033</t>
+          <t>924426</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1748299</t>
+          <t>1743036</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1891104</t>
+          <t>1882937</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,34%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1492165</t>
+          <t>1487401</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1607027</t>
+          <t>1604839</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1828775</t>
+          <t>1829729</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1947740</t>
+          <t>1940226</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3348036</t>
+          <t>3338828</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3518048</t>
+          <t>3509952</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,83%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de fruta fresca en 2012</t>
+          <t>Población según la frecuencia de consumo de fruta fresca (excluyendo zumos) en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2948</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15075</t>
+          <t>15384</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11896</t>
+          <t>12535</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>6973</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23260</t>
+          <t>23007</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21294</t>
+          <t>20212</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9270</t>
+          <t>10386</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8282</t>
+          <t>8777</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24525</t>
+          <t>26927</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36724</t>
+          <t>36387</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64580</t>
+          <t>63954</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10274</t>
+          <t>10384</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29131</t>
+          <t>29908</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52980</t>
+          <t>51194</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>84032</t>
+          <t>85205</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>99890</t>
+          <t>97798</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>138802</t>
+          <t>139164</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52787</t>
+          <t>53139</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83175</t>
+          <t>82673</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>161900</t>
+          <t>162000</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>209588</t>
+          <t>212527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>229468</t>
+          <t>229825</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>272053</t>
+          <t>272731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>200063</t>
+          <t>199726</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>234272</t>
+          <t>234716</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>442843</t>
+          <t>439087</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>496932</t>
+          <t>497092</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,23%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20975</t>
+          <t>20345</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27519</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>7206</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21322</t>
+          <t>22440</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18332</t>
+          <t>18192</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14633</t>
+          <t>15222</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34994</t>
+          <t>34048</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29933</t>
+          <t>30559</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58653</t>
+          <t>56295</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13992</t>
+          <t>14736</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31648</t>
+          <t>32069</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49096</t>
+          <t>49951</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>80776</t>
+          <t>83748</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84333</t>
+          <t>85827</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122664</t>
+          <t>122855</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64790</t>
+          <t>64514</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97573</t>
+          <t>98153</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157325</t>
+          <t>158740</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>207573</t>
+          <t>208881</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,71%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>234186</t>
+          <t>233596</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>277459</t>
+          <t>277610</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192996</t>
+          <t>193205</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>229679</t>
+          <t>230604</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>440351</t>
+          <t>439974</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>494965</t>
+          <t>496978</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,94%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8436</t>
+          <t>8536</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23059</t>
+          <t>23482</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>13210</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>11539</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30035</t>
+          <t>29842</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>14113</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33095</t>
+          <t>33656</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12382</t>
+          <t>12499</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18240</t>
+          <t>18127</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41102</t>
+          <t>41412</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>60435</t>
+          <t>61340</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>94431</t>
+          <t>97508</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17633</t>
+          <t>15921</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36022</t>
+          <t>34708</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>83559</t>
+          <t>83023</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>120504</t>
+          <t>121183</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>102053</t>
+          <t>101052</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>142356</t>
+          <t>141463</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30100</t>
+          <t>31128</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54698</t>
+          <t>55488</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>140797</t>
+          <t>140861</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>189070</t>
+          <t>187876</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>370344</t>
+          <t>369905</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>420492</t>
+          <t>420125</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>167124</t>
+          <t>166604</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>197673</t>
+          <t>196684</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>544639</t>
+          <t>548300</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>606723</t>
+          <t>607742</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,32%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40572</t>
+          <t>40526</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>11637</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30553</t>
+          <t>30844</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33944</t>
+          <t>34487</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63892</t>
+          <t>64825</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16384</t>
+          <t>16756</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35311</t>
+          <t>35841</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13099</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>35380</t>
+          <t>34967</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>35730</t>
+          <t>34376</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>63508</t>
+          <t>62860</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>87300</t>
+          <t>87887</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>128375</t>
+          <t>129995</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52473</t>
+          <t>51669</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>84538</t>
+          <t>85059</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>149748</t>
+          <t>151042</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>202581</t>
+          <t>203863</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>237857</t>
+          <t>236983</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>296276</t>
+          <t>295695</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>131536</t>
+          <t>132760</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>176089</t>
+          <t>177734</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>383335</t>
+          <t>381360</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>456274</t>
+          <t>453466</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>699524</t>
+          <t>700633</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>766887</t>
+          <t>772676</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>472376</t>
+          <t>473243</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>528230</t>
+          <t>527010</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1190312</t>
+          <t>1190861</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1276655</t>
+          <t>1277488</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,48%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22550</t>
+          <t>22362</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22512</t>
+          <t>20535</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16248</t>
+          <t>15651</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>37300</t>
+          <t>37292</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>15671</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>37574</t>
+          <t>35822</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19204</t>
+          <t>19695</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>43187</t>
+          <t>42612</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41009</t>
+          <t>40350</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>72286</t>
+          <t>70049</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>44504</t>
+          <t>43816</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>70631</t>
+          <t>72439</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>41064</t>
+          <t>41971</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>68708</t>
+          <t>69420</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>93544</t>
+          <t>91284</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>134742</t>
+          <t>131765</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>103239</t>
+          <t>103273</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>140342</t>
+          <t>141362</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>124164</t>
+          <t>123570</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>168094</t>
+          <t>166515</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>236093</t>
+          <t>239097</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>293615</t>
+          <t>297973</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>269055</t>
+          <t>269681</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>313714</t>
+          <t>313853</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>496941</t>
+          <t>496846</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>549177</t>
+          <t>546751</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>778769</t>
+          <t>778970</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>847849</t>
+          <t>847041</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,69%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13133</t>
+          <t>13047</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7913</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>24173</t>
+          <t>23761</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>13576</t>
+          <t>13733</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>31543</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>21358</t>
+          <t>21017</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>15546</t>
+          <t>14774</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>35614</t>
+          <t>35145</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>25098</t>
+          <t>25946</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>49931</t>
+          <t>52121</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>39254</t>
+          <t>39505</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>65676</t>
+          <t>64998</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>66956</t>
+          <t>65162</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>100297</t>
+          <t>102809</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>113392</t>
+          <t>114752</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>159408</t>
+          <t>159206</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>64681</t>
+          <t>64325</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>94792</t>
+          <t>93738</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>191183</t>
+          <t>192961</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>245020</t>
+          <t>247072</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>265949</t>
+          <t>262570</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>325940</t>
+          <t>327994</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>99813</t>
+          <t>101179</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>132031</t>
+          <t>133861</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>736565</t>
+          <t>736839</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>795491</t>
+          <t>801127</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>852784</t>
+          <t>848804</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>922834</t>
+          <t>923614</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,22%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>58727</t>
+          <t>58729</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>92499</t>
+          <t>94508</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>53269</t>
+          <t>53195</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>87340</t>
+          <t>88132</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>119071</t>
+          <t>118097</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>167806</t>
+          <t>168746</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>89523</t>
+          <t>88166</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>131033</t>
+          <t>130702</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>76253</t>
+          <t>78383</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>116979</t>
+          <t>119137</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>177180</t>
+          <t>177689</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>239331</t>
+          <t>237894</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>345098</t>
+          <t>346266</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>422639</t>
+          <t>425735</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>239065</t>
+          <t>238876</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>306852</t>
+          <t>304481</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>604147</t>
+          <t>604950</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>704033</t>
+          <t>705561</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>758727</t>
+          <t>759945</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>863869</t>
+          <t>864238</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>653081</t>
+          <t>651792</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>752351</t>
+          <t>755062</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1438715</t>
+          <t>1436997</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1581458</t>
+          <t>1583551</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1984675</t>
+          <t>1983205</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2108554</t>
+          <t>2098158</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2350449</t>
+          <t>2347567</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2465323</t>
+          <t>2463127</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4364375</t>
+          <t>4361677</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4533938</t>
+          <t>4536333</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de fruta fresca en 2016</t>
+          <t>Población según la frecuencia de consumo de fruta fresca (excluyendo zumos) en 2016 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16610</t>
+          <t>15949</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>922</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7578</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19540</t>
+          <t>20414</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24234</t>
+          <t>22764</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>11925</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>11950</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30835</t>
+          <t>31061</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38782</t>
+          <t>37732</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68059</t>
+          <t>69394</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30945</t>
+          <t>29595</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54427</t>
+          <t>54096</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>76313</t>
+          <t>75024</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>113359</t>
+          <t>114158</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84951</t>
+          <t>83805</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>121788</t>
+          <t>120822</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71320</t>
+          <t>71845</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105389</t>
+          <t>104214</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>163890</t>
+          <t>166928</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>212710</t>
+          <t>214218</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,6%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>231525</t>
+          <t>230423</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>274851</t>
+          <t>274333</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>190530</t>
+          <t>190628</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>228191</t>
+          <t>227451</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>434794</t>
+          <t>433278</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>489430</t>
+          <t>492300</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,43%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16552</t>
+          <t>16488</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4411</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16660</t>
+          <t>17259</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11134</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28479</t>
+          <t>28893</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12183</t>
+          <t>12623</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16669</t>
+          <t>15906</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>7920</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22850</t>
+          <t>22768</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34014</t>
+          <t>32371</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58987</t>
+          <t>58170</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38229</t>
+          <t>38327</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65803</t>
+          <t>65016</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>77187</t>
+          <t>79002</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>114766</t>
+          <t>114852</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91176</t>
+          <t>91762</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128156</t>
+          <t>127773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83996</t>
+          <t>83722</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118125</t>
+          <t>118802</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>184459</t>
+          <t>184039</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>235521</t>
+          <t>235315</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,55%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>188552</t>
+          <t>187560</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>226602</t>
+          <t>227517</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>182088</t>
+          <t>179901</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>220529</t>
+          <t>219331</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>382484</t>
+          <t>378931</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>436913</t>
+          <t>436697</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,55%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9367</t>
+          <t>9002</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25277</t>
+          <t>24152</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>860</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11900</t>
+          <t>11472</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29426</t>
+          <t>28677</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17671</t>
+          <t>18036</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39725</t>
+          <t>40787</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20474</t>
+          <t>18863</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43122</t>
+          <t>41238</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52780</t>
+          <t>52493</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85276</t>
+          <t>84573</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12354</t>
+          <t>12432</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28700</t>
+          <t>29773</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>71130</t>
+          <t>69004</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>106205</t>
+          <t>105250</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>131716</t>
+          <t>130060</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>173768</t>
+          <t>172043</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31503</t>
+          <t>31925</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55210</t>
+          <t>55520</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>170087</t>
+          <t>168622</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>217196</t>
+          <t>216118</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235211</t>
+          <t>236502</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>281591</t>
+          <t>280318</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>85443</t>
+          <t>84320</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>111832</t>
+          <t>110766</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>330199</t>
+          <t>333106</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>384583</t>
+          <t>384190</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,07%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14054</t>
+          <t>14579</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34213</t>
+          <t>34665</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15010</t>
+          <t>14904</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34258</t>
+          <t>34243</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,7 +12844,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33604</t>
+          <t>32367</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61298</t>
+          <t>59264</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31724</t>
+          <t>31648</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>59523</t>
+          <t>57395</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25167</t>
+          <t>26336</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>51603</t>
+          <t>52098</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>64621</t>
+          <t>64632</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>101860</t>
+          <t>99438</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>131926</t>
+          <t>132461</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>178667</t>
+          <t>180804</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>97028</t>
+          <t>95819</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>136890</t>
+          <t>137756</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>242215</t>
+          <t>238920</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>304348</t>
+          <t>299126</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>332712</t>
+          <t>331747</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>395542</t>
+          <t>394027</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>216611</t>
+          <t>214571</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>270323</t>
+          <t>267262</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>562460</t>
+          <t>562428</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>647530</t>
+          <t>643288</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,61%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>530303</t>
+          <t>530438</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>597982</t>
+          <t>597818</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>378327</t>
+          <t>375949</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>437365</t>
+          <t>437029</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>925394</t>
+          <t>924365</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1016945</t>
+          <t>1016017</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,51%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10439</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>29073</t>
+          <t>30248</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>8726</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23399</t>
+          <t>24026</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>22278</t>
+          <t>22170</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>46174</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13722</t>
+          <t>14319</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>32615</t>
+          <t>33047</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13499</t>
+          <t>13439</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>31648</t>
+          <t>30862</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>33156</t>
+          <t>32529</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>58643</t>
+          <t>58589</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>66641</t>
+          <t>65585</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>101467</t>
+          <t>100337</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>57003</t>
+          <t>57520</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>88695</t>
+          <t>89803</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>133129</t>
+          <t>131913</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>179386</t>
+          <t>181918</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>168604</t>
+          <t>165047</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>214241</t>
+          <t>212261</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>203113</t>
+          <t>202997</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>254287</t>
+          <t>254885</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>382340</t>
+          <t>386516</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>452381</t>
+          <t>455610</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,55%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>285393</t>
+          <t>282775</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>334031</t>
+          <t>333350</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>371275</t>
+          <t>372592</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>426078</t>
+          <t>426792</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>669907</t>
+          <t>671421</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>745354</t>
+          <t>747924</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,08%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6970</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>20489</t>
+          <t>19751</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>11256</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>30399</t>
+          <t>29473</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>21094</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>43682</t>
+          <t>43351</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26518</t>
+          <t>27708</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>29084</t>
+          <t>28813</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>54724</t>
+          <t>53365</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>43222</t>
+          <t>43159</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>73573</t>
+          <t>73571</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>43584</t>
+          <t>42073</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>69763</t>
+          <t>70119</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>82754</t>
+          <t>82463</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>120387</t>
+          <t>121995</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>134987</t>
+          <t>135199</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>182242</t>
+          <t>181576</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>77992</t>
+          <t>75953</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>108450</t>
+          <t>108533</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>243915</t>
+          <t>245054</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>303654</t>
+          <t>304657</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>330195</t>
+          <t>330081</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>398743</t>
+          <t>399786</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,24%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>92498</t>
+          <t>92954</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>125115</t>
+          <t>128387</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>613332</t>
+          <t>614890</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>679554</t>
+          <t>680092</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>723116</t>
+          <t>719051</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>794987</t>
+          <t>794944</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,14%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>67540</t>
+          <t>69681</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>105064</t>
+          <t>106145</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>57115</t>
+          <t>55132</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>91145</t>
+          <t>89728</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>134565</t>
+          <t>134142</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>183928</t>
+          <t>182062</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>107675</t>
+          <t>108603</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>153394</t>
+          <t>153782</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>95617</t>
+          <t>95155</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>139107</t>
+          <t>138436</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>213047</t>
+          <t>212254</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>276321</t>
+          <t>278155</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>417345</t>
+          <t>420328</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>497997</t>
+          <t>502067</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>364748</t>
+          <t>367242</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>441378</t>
+          <t>437966</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>804985</t>
+          <t>801694</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>911976</t>
+          <t>917226</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>950567</t>
+          <t>952396</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1059019</t>
+          <t>1053546</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>915386</t>
+          <t>920861</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1030116</t>
+          <t>1028830</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1905477</t>
+          <t>1897690</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2055206</t>
+          <t>2058126</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,81%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1635241</t>
+          <t>1642836</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1757624</t>
+          <t>1755551</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1903976</t>
+          <t>1908425</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2029355</t>
+          <t>2026046</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3578589</t>
+          <t>3581494</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3752383</t>
+          <t>3749381</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,3%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B06-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B06-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17670</t>
+          <t>18843</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>7167</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20234</t>
+          <t>20604</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>13232</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30569</t>
+          <t>31782</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17992</t>
+          <t>17019</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19778</t>
+          <t>20977</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41942</t>
+          <t>41974</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49546</t>
+          <t>50759</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80250</t>
+          <t>79399</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25409</t>
+          <t>25645</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47541</t>
+          <t>48008</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82581</t>
+          <t>82446</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>120798</t>
+          <t>121722</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>114864</t>
+          <t>114442</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154785</t>
+          <t>153152</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72056</t>
+          <t>72808</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104873</t>
+          <t>104399</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>196952</t>
+          <t>195993</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>247162</t>
+          <t>247565</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>225159</t>
+          <t>225209</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>269283</t>
+          <t>267814</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>150041</t>
+          <t>154205</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>187108</t>
+          <t>189784</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>389409</t>
+          <t>391534</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>444366</t>
+          <t>447670</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>57,36%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13838</t>
+          <t>15065</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20923</t>
+          <t>22699</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>12258</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30587</t>
+          <t>30909</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>12022</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30198</t>
+          <t>29690</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22407</t>
+          <t>21016</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21993</t>
+          <t>22288</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44299</t>
+          <t>43909</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>39995</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65953</t>
+          <t>65730</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42531</t>
+          <t>42312</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70254</t>
+          <t>70675</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>87799</t>
+          <t>88579</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124915</t>
+          <t>127133</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87263</t>
+          <t>89698</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122776</t>
+          <t>125415</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83945</t>
+          <t>85548</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117408</t>
+          <t>119081</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>180160</t>
+          <t>184182</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>231240</t>
+          <t>231793</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,41%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>163195</t>
+          <t>162890</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>202140</t>
+          <t>203036</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>169376</t>
+          <t>168818</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>209306</t>
+          <t>207974</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>346308</t>
+          <t>344998</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>401796</t>
+          <t>401020</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,34%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22506</t>
+          <t>20728</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2311</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>13008</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>12462</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28893</t>
+          <t>30005</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22348</t>
+          <t>21945</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>44825</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>961</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11552</t>
+          <t>11263</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24446</t>
+          <t>26180</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51443</t>
+          <t>49055</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67451</t>
+          <t>66117</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100888</t>
+          <t>99766</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13563</t>
+          <t>12798</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31764</t>
+          <t>30403</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>86706</t>
+          <t>85357</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>124554</t>
+          <t>124300</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>141446</t>
+          <t>140664</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>185495</t>
+          <t>184440</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34350</t>
+          <t>35506</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57720</t>
+          <t>58604</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>183761</t>
+          <t>185062</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>234401</t>
+          <t>234712</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>229028</t>
+          <t>229744</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>276275</t>
+          <t>276267</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>77849</t>
+          <t>77074</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>102598</t>
+          <t>103537</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>315656</t>
+          <t>315411</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>368867</t>
+          <t>370236</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,13%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12844</t>
+          <t>13437</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32201</t>
+          <t>32618</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20505</t>
+          <t>19914</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22400</t>
+          <t>22815</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46669</t>
+          <t>46044</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>52271</t>
+          <t>52031</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>85739</t>
+          <t>84853</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,82 +2906,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>6,86%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>34453</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>25261</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>47421</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>6,64%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>101206</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>82292</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>123657</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>4,22%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>34453</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>24599</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>47849</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>6,7%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>101206</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>82373</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>121958</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>168502</t>
+          <t>167024</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>219138</t>
+          <t>218541</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>70733</t>
+          <t>69441</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>105075</t>
+          <t>105893</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>249648</t>
+          <t>253819</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>314724</t>
+          <t>312157</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>308352</t>
+          <t>308575</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>374487</t>
+          <t>373235</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,82 +3132,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>24,94%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>30,16%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>184089</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>161171</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>209959</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>25,77%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>22,56%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>29,39%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>524151</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>486368</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>566297</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>26,86%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>24,92%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>30,26%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>184089</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>160239</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>205984</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>25,77%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>22,43%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>28,84%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>524151</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>483245</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>563782</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>26,86%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>24,76%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>579398</t>
+          <t>578923</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>650267</t>
+          <t>650456</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>368984</t>
+          <t>370697</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>422794</t>
+          <t>425646</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>966090</t>
+          <t>966525</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1052651</t>
+          <t>1051536</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,88%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>6769</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22078</t>
+          <t>23071</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19530</t>
+          <t>19024</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>15302</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>35672</t>
+          <t>37102</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14929</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34372</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11006</t>
+          <t>11564</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28608</t>
+          <t>29677</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>29735</t>
+          <t>29474</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>55519</t>
+          <t>55031</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>55664</t>
+          <t>53078</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>85521</t>
+          <t>84092</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>68163</t>
+          <t>67278</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>101096</t>
+          <t>100886</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>131706</t>
+          <t>128050</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>176595</t>
+          <t>175755</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>86364</t>
+          <t>87873</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>120108</t>
+          <t>123775</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>131112</t>
+          <t>131994</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>174112</t>
+          <t>173961</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>230638</t>
+          <t>228948</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>283900</t>
+          <t>286687</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>124695</t>
+          <t>122652</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>159498</t>
+          <t>161628</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>275640</t>
+          <t>278203</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>323670</t>
+          <t>325276</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>414212</t>
+          <t>412646</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>473013</t>
+          <t>474619</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,69%</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7030</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21041</t>
+          <t>20432</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>11879</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>28214</t>
+          <t>27681</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>21372</t>
+          <t>21634</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>43781</t>
+          <t>43495</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>17722</t>
+          <t>17717</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>36173</t>
+          <t>35767</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>21706</t>
+          <t>22950</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>43120</t>
+          <t>44894</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>45218</t>
+          <t>46064</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>73583</t>
+          <t>74264</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>44546</t>
+          <t>45813</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>71619</t>
+          <t>71126</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>138524</t>
+          <t>138685</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>185212</t>
+          <t>185702</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>191476</t>
+          <t>192442</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>245857</t>
+          <t>245935</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>78933</t>
+          <t>79123</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>110713</t>
+          <t>111421</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>271380</t>
+          <t>267623</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>329869</t>
+          <t>329707</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>358610</t>
+          <t>363106</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>427206</t>
+          <t>428144</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,71%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>90966</t>
+          <t>92563</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>123255</t>
+          <t>124037</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>698831</t>
+          <t>702285</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>765462</t>
+          <t>769938</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>807866</t>
+          <t>805200</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>884255</t>
+          <t>880736</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,01%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>58535</t>
+          <t>56829</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>92980</t>
+          <t>91876</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>48462</t>
+          <t>49260</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>80301</t>
+          <t>80729</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>115073</t>
+          <t>114451</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>161661</t>
+          <t>163592</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>162186</t>
+          <t>158600</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>215276</t>
+          <t>214233</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>92887</t>
+          <t>92608</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>134057</t>
+          <t>133626</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>268129</t>
+          <t>268018</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>335140</t>
+          <t>334676</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>477838</t>
+          <t>476585</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>564063</t>
+          <t>562607</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>407156</t>
+          <t>408075</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>483235</t>
+          <t>485967</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>906167</t>
+          <t>905727</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1022088</t>
+          <t>1022135</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>888126</t>
+          <t>887631</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>992544</t>
+          <t>996000</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>827480</t>
+          <t>820856</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>924426</t>
+          <t>922931</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1743036</t>
+          <t>1738715</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1882937</t>
+          <t>1885239</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,38%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1487401</t>
+          <t>1491361</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1604839</t>
+          <t>1607767</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1829729</t>
+          <t>1826279</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1940226</t>
+          <t>1941508</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3338828</t>
+          <t>3356255</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3509952</t>
+          <t>3521972</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>53,01%</t>
         </is>
       </c>
     </row>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15384</t>
+          <t>16235</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12535</t>
+          <t>11855</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23007</t>
+          <t>22576</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20212</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,82 +5868,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4128</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>9430</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>15323</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>8640</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>26244</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>4128</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10386</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>15323</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>8777</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>26927</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36387</t>
+          <t>37475</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63954</t>
+          <t>65237</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10384</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29908</t>
+          <t>30033</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>51194</t>
+          <t>52694</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>85205</t>
+          <t>87195</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>97798</t>
+          <t>100434</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>139164</t>
+          <t>140103</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53139</t>
+          <t>52741</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82673</t>
+          <t>81699</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>162000</t>
+          <t>161731</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>212527</t>
+          <t>211509</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>229825</t>
+          <t>227576</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>272731</t>
+          <t>270415</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>199726</t>
+          <t>202777</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>234716</t>
+          <t>235994</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>439087</t>
+          <t>443131</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>497092</t>
+          <t>497531</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,29%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10755</t>
+          <t>10348</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20345</t>
+          <t>20242</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>9825</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26628</t>
+          <t>26181</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22440</t>
+          <t>21600</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18192</t>
+          <t>17858</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15222</t>
+          <t>14890</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34048</t>
+          <t>36391</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30559</t>
+          <t>30039</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56295</t>
+          <t>56138</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14736</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32069</t>
+          <t>32524</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49951</t>
+          <t>50259</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83748</t>
+          <t>80689</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85827</t>
+          <t>84304</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122855</t>
+          <t>122712</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64514</t>
+          <t>64026</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98153</t>
+          <t>98088</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>158740</t>
+          <t>157583</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>208881</t>
+          <t>208990</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>233596</t>
+          <t>233893</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>277610</t>
+          <t>276402</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>193205</t>
+          <t>193869</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>230604</t>
+          <t>230699</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>439974</t>
+          <t>436285</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>496978</t>
+          <t>494342</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,59%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>7987</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23482</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13210</t>
+          <t>13292</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11539</t>
+          <t>11913</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29842</t>
+          <t>30363</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14113</t>
+          <t>13270</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33656</t>
+          <t>32833</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12499</t>
+          <t>12523</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18127</t>
+          <t>17877</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41412</t>
+          <t>41005</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61340</t>
+          <t>59019</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>97508</t>
+          <t>94754</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15921</t>
+          <t>16675</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34708</t>
+          <t>37162</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>83023</t>
+          <t>82150</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>121183</t>
+          <t>120769</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>101052</t>
+          <t>102390</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>141463</t>
+          <t>142899</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31128</t>
+          <t>29322</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55488</t>
+          <t>54566</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>140861</t>
+          <t>140777</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>187876</t>
+          <t>190268</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>369905</t>
+          <t>369153</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>420125</t>
+          <t>419429</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>166604</t>
+          <t>167023</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>196684</t>
+          <t>197786</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>548300</t>
+          <t>548107</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>607742</t>
+          <t>605046</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,02%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17746</t>
+          <t>18591</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40526</t>
+          <t>41460</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>11936</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30844</t>
+          <t>30758</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34487</t>
+          <t>32941</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64825</t>
+          <t>62872</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16756</t>
+          <t>16913</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35841</t>
+          <t>36090</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13925</t>
+          <t>13407</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34967</t>
+          <t>35733</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>34376</t>
+          <t>34757</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>62860</t>
+          <t>63071</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>87887</t>
+          <t>89197</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>129995</t>
+          <t>130395</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>51669</t>
+          <t>51772</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>85059</t>
+          <t>84197</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>151042</t>
+          <t>150471</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>203863</t>
+          <t>202989</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>236983</t>
+          <t>235253</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>295695</t>
+          <t>293888</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>132760</t>
+          <t>131764</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>177734</t>
+          <t>178962</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>381360</t>
+          <t>383712</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>453466</t>
+          <t>456008</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>700633</t>
+          <t>698934</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>772676</t>
+          <t>766190</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>473243</t>
+          <t>473336</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>527010</t>
+          <t>528547</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1190861</t>
+          <t>1190355</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1277488</t>
+          <t>1273722</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,28%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8356</t>
+          <t>7669</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>24132</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20535</t>
+          <t>21373</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15651</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>37292</t>
+          <t>37142</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15671</t>
+          <t>16571</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35822</t>
+          <t>36033</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19695</t>
+          <t>19764</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>42612</t>
+          <t>42712</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>40350</t>
+          <t>41598</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>70049</t>
+          <t>72255</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>43816</t>
+          <t>43696</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>72439</t>
+          <t>72213</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>41971</t>
+          <t>40530</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>69420</t>
+          <t>70502</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>91284</t>
+          <t>93718</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>131765</t>
+          <t>133913</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>103273</t>
+          <t>102640</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>141362</t>
+          <t>140097</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>123570</t>
+          <t>122373</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>166515</t>
+          <t>169265</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>239097</t>
+          <t>238208</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>297973</t>
+          <t>295074</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>269681</t>
+          <t>268011</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>313853</t>
+          <t>312372</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>496846</t>
+          <t>495973</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>546751</t>
+          <t>549257</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>778970</t>
+          <t>780883</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>847041</t>
+          <t>847529</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,73%</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13047</t>
+          <t>12580</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>8767</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23761</t>
+          <t>26131</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>13733</t>
+          <t>13741</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>31601</t>
+          <t>31430</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>7493</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>21017</t>
+          <t>22303</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>14774</t>
+          <t>15001</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>35145</t>
+          <t>34736</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>25946</t>
+          <t>25278</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>52121</t>
+          <t>50145</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>39505</t>
+          <t>40133</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>64998</t>
+          <t>64819</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>65162</t>
+          <t>66769</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>102809</t>
+          <t>104000</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>114752</t>
+          <t>113125</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>159206</t>
+          <t>156052</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>64325</t>
+          <t>65080</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>93738</t>
+          <t>92980</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>192961</t>
+          <t>192887</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>247072</t>
+          <t>244651</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>262570</t>
+          <t>265810</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>327994</t>
+          <t>328449</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>101179</t>
+          <t>101187</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>133861</t>
+          <t>132621</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>736839</t>
+          <t>737631</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>801127</t>
+          <t>797936</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>848804</t>
+          <t>848545</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>923614</t>
+          <t>920457</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>66,99%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>58729</t>
+          <t>57562</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>94508</t>
+          <t>93212</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>53195</t>
+          <t>51976</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>88132</t>
+          <t>86565</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>118097</t>
+          <t>119054</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>168746</t>
+          <t>166472</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>88166</t>
+          <t>89689</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>130702</t>
+          <t>132819</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>78383</t>
+          <t>75486</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>119137</t>
+          <t>117519</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>177689</t>
+          <t>175370</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>237894</t>
+          <t>230983</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>346266</t>
+          <t>345132</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>425735</t>
+          <t>420942</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>238876</t>
+          <t>237872</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>304481</t>
+          <t>303959</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>604950</t>
+          <t>605749</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>705561</t>
+          <t>707454</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>759945</t>
+          <t>759643</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>864238</t>
+          <t>860588</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>651792</t>
+          <t>653517</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>755062</t>
+          <t>751483</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1436997</t>
+          <t>1436022</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1583551</t>
+          <t>1584218</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1983205</t>
+          <t>1981071</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2098158</t>
+          <t>2097967</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2347567</t>
+          <t>2345818</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2463127</t>
+          <t>2464221</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4361677</t>
+          <t>4354159</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4536333</t>
+          <t>4526639</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,04%</t>
         </is>
       </c>
     </row>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15949</t>
+          <t>15787</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10768,7 +10768,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>919</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7823</t>
+          <t>8406</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20414</t>
+          <t>19499</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>6898</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22764</t>
+          <t>22009</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11925</t>
+          <t>12113</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11950</t>
+          <t>11583</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31061</t>
+          <t>30508</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37732</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69394</t>
+          <t>69251</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29595</t>
+          <t>30095</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54096</t>
+          <t>54655</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>75024</t>
+          <t>76109</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>114158</t>
+          <t>115515</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83805</t>
+          <t>85866</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>120822</t>
+          <t>122337</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71845</t>
+          <t>73237</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104214</t>
+          <t>106115</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>166928</t>
+          <t>168332</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>214218</t>
+          <t>215869</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>230423</t>
+          <t>229564</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>274333</t>
+          <t>273567</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>190628</t>
+          <t>191075</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>227451</t>
+          <t>226487</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>433278</t>
+          <t>432380</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>492300</t>
+          <t>488282</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>62,91%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16488</t>
+          <t>16867</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17259</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>10936</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28893</t>
+          <t>28682</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12623</t>
+          <t>11882</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15906</t>
+          <t>15759</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>7817</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22768</t>
+          <t>22684</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32371</t>
+          <t>33017</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58170</t>
+          <t>60550</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38327</t>
+          <t>38345</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65016</t>
+          <t>66345</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>79002</t>
+          <t>78513</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>114852</t>
+          <t>113982</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91762</t>
+          <t>91244</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127773</t>
+          <t>127243</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83722</t>
+          <t>81325</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118802</t>
+          <t>116721</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>184039</t>
+          <t>185692</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>235315</t>
+          <t>237218</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>187560</t>
+          <t>186149</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>227517</t>
+          <t>227112</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>179901</t>
+          <t>182117</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>219331</t>
+          <t>223252</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>378931</t>
+          <t>380688</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>436697</t>
+          <t>435981</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,45%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24152</t>
+          <t>25264</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>889</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>8799</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11472</t>
+          <t>11199</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28677</t>
+          <t>28954</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18036</t>
+          <t>18268</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40787</t>
+          <t>39245</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6842</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18863</t>
+          <t>19665</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41238</t>
+          <t>41228</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52493</t>
+          <t>53517</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84573</t>
+          <t>83963</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>12991</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29773</t>
+          <t>31168</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>69004</t>
+          <t>71253</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>105250</t>
+          <t>105846</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>130060</t>
+          <t>129948</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>172043</t>
+          <t>172569</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31925</t>
+          <t>31308</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55520</t>
+          <t>54674</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>168622</t>
+          <t>169132</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>216118</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236502</t>
+          <t>234509</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>280318</t>
+          <t>281981</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84320</t>
+          <t>85382</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110766</t>
+          <t>111303</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>333106</t>
+          <t>329228</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>384190</t>
+          <t>384037</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,04%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>14678</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34665</t>
+          <t>35281</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>15176</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34243</t>
+          <t>33961</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32367</t>
+          <t>33570</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59264</t>
+          <t>60837</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31648</t>
+          <t>33104</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>57395</t>
+          <t>59091</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26336</t>
+          <t>27107</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>52098</t>
+          <t>52549</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>64632</t>
+          <t>63361</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>99438</t>
+          <t>101275</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>132461</t>
+          <t>135526</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>180804</t>
+          <t>180066</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>95819</t>
+          <t>98002</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>137756</t>
+          <t>136586</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>238920</t>
+          <t>242404</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>299126</t>
+          <t>304356</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>331747</t>
+          <t>331110</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>394027</t>
+          <t>393470</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>214571</t>
+          <t>217281</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>267262</t>
+          <t>266589</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>562428</t>
+          <t>560601</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>643288</t>
+          <t>645694</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>530438</t>
+          <t>529302</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>597818</t>
+          <t>596969</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>375949</t>
+          <t>379098</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>437029</t>
+          <t>435656</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>924365</t>
+          <t>929227</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1016017</t>
+          <t>1019549</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,69%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10439</t>
+          <t>9696</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>30248</t>
+          <t>28620</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8726</t>
+          <t>8855</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>24026</t>
+          <t>24398</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>22170</t>
+          <t>22603</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>45909</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14319</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>33047</t>
+          <t>33738</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13439</t>
+          <t>13796</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30862</t>
+          <t>32063</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32529</t>
+          <t>32769</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>58589</t>
+          <t>58626</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>65585</t>
+          <t>66670</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>100337</t>
+          <t>100194</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>57520</t>
+          <t>56440</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>89803</t>
+          <t>90070</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>131913</t>
+          <t>131962</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>181918</t>
+          <t>179575</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>165047</t>
+          <t>169259</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>212261</t>
+          <t>212341</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>202997</t>
+          <t>204553</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>254885</t>
+          <t>253475</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>386516</t>
+          <t>386798</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>455610</t>
+          <t>451796</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>282775</t>
+          <t>285608</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>333350</t>
+          <t>332551</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>372592</t>
+          <t>374723</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>426792</t>
+          <t>429788</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>671421</t>
+          <t>672347</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>747924</t>
+          <t>745353</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,89%</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>19751</t>
+          <t>20437</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>11532</t>
+          <t>11666</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>29473</t>
+          <t>29663</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>20823</t>
+          <t>21321</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>43351</t>
+          <t>43423</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>27708</t>
+          <t>27456</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>28813</t>
+          <t>28695</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>53365</t>
+          <t>54490</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>43159</t>
+          <t>43873</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>73571</t>
+          <t>73610</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,7 +14356,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>42073</t>
+          <t>43446</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>70119</t>
+          <t>71468</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>82463</t>
+          <t>83022</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>121995</t>
+          <t>122843</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>135199</t>
+          <t>133286</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>181576</t>
+          <t>181006</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>75953</t>
+          <t>75920</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>108533</t>
+          <t>108437</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>245054</t>
+          <t>246242</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>304657</t>
+          <t>306145</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>330081</t>
+          <t>329510</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>399786</t>
+          <t>397954</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>92954</t>
+          <t>94861</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>128387</t>
+          <t>127126</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>614890</t>
+          <t>611821</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>680092</t>
+          <t>679168</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>719051</t>
+          <t>722326</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>794944</t>
+          <t>800160</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,53%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>69681</t>
+          <t>69856</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>106145</t>
+          <t>108768</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>55132</t>
+          <t>55681</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>89728</t>
+          <t>87648</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>134142</t>
+          <t>133290</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>182062</t>
+          <t>182586</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>108603</t>
+          <t>106800</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>153782</t>
+          <t>152579</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>95155</t>
+          <t>93888</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>138436</t>
+          <t>137621</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>212254</t>
+          <t>216774</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>278155</t>
+          <t>275763</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>420328</t>
+          <t>419801</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>502067</t>
+          <t>499265</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,82 +15081,82 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
+          <t>12,42%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>14,78%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>400380</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>365245</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>443901</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>11,36%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>12,59%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>858826</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>811057</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>921809</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
           <t>12,44%</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>14,86%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>400380</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>367242</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>437966</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>11,36%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>10,42%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>12,42%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>810</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>858826</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>801694</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>917226</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>12,44%</t>
-        </is>
-      </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>952396</t>
+          <t>951880</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1053546</t>
+          <t>1058757</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>920861</t>
+          <t>919462</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1028830</t>
+          <t>1025902</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1897690</t>
+          <t>1900920</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2058126</t>
+          <t>2058380</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1642836</t>
+          <t>1643294</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1755551</t>
+          <t>1761457</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1908425</t>
+          <t>1905293</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2026046</t>
+          <t>2024234</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3581494</t>
+          <t>3582461</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3749381</t>
+          <t>3752843</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,35%</t>
         </is>
       </c>
     </row>
